--- a/src/attributions/attributions_ig_traj_410.xlsx
+++ b/src/attributions/attributions_ig_traj_410.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG12"/>
+  <dimension ref="A1:GG20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2137,37 +2137,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.04282373121251561</v>
+        <v>0.1842030246995134</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-7.975097701547876e-05</v>
+        <v>0.03736722272489271</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.02221005193699549</v>
+        <v>-0.1005958789442198</v>
       </c>
       <c r="G4" t="n">
         <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02605423869585583</v>
+        <v>0.2629527308519106</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,133 +2176,133 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01169165969599973</v>
+        <v>-0.039486246462797</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0479364268046837</v>
+        <v>-0.2021462931044934</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0009626625489587377</v>
+        <v>-0.003273723794830437</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.002125694473780322</v>
+        <v>-0.01783406741646096</v>
       </c>
       <c r="X4" t="n">
-        <v>1.022523344815992e-11</v>
+        <v>-7.932929085170956e-11</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01137672227920239</v>
+        <v>0.0193539122745509</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.04516240191989626</v>
+        <v>-0.05970590078258891</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0009998532181612727</v>
+        <v>0.1462099866770577</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.006097387961814871</v>
+        <v>0.1044203352484421</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.0153737926629049</v>
+        <v>-0.07415641180643309</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.01816927918288667</v>
+        <v>-0.1329735122202889</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.04714041395235369</v>
+        <v>0.3729668997559196</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.009178238547966826</v>
+        <v>-0.1660057915365042</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.03438186335389386</v>
+        <v>-0.2921594692310132</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.02319315839329508</v>
+        <v>0.03334286330243807</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,70 +2311,70 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.02471024685279252</v>
+        <v>0.01650210894394082</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.0231193327398631</v>
+        <v>-0.05467257677777147</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.02339310509560655</v>
+        <v>0.09458657704243292</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.0008865517510596796</v>
+        <v>0.0824018323100163</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.008740031589505308</v>
+        <v>0.1431622721698501</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
         <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.03631645764438466</v>
+        <v>0.2806881405462287</v>
       </c>
       <c r="BW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.01386057364079277</v>
+        <v>-0.1181636098943544</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.01619039915183042</v>
+        <v>-0.3651435418306747</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.01479072256459702</v>
+        <v>-0.1765943036885395</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
@@ -2392,37 +2392,37 @@
         <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.005148663647879538</v>
+        <v>-0.07025293658101534</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.03296239478898019</v>
+        <v>0.1784822010897162</v>
       </c>
       <c r="CJ4" t="n">
         <v>0</v>
       </c>
       <c r="CK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0106679824886312</v>
+        <v>-0.1627614702348974</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.01197754190531564</v>
+        <v>0.07594978459690734</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.005500653442874022</v>
+        <v>0.1056189951270684</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
@@ -2434,10 +2434,10 @@
         <v>0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.01011242226511502</v>
+        <v>-0.1620721284105474</v>
       </c>
       <c r="CX4" t="n">
         <v>0</v>
@@ -2446,133 +2446,133 @@
         <v>0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.007987515496235349</v>
+        <v>-0.04927867594948016</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.03190112062528697</v>
+        <v>0.1709112325559453</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.02760209441755812</v>
+        <v>-0.1492672793536948</v>
       </c>
       <c r="DG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH4" t="n">
         <v>-0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.02026679299030058</v>
+        <v>-0.1511964596312615</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.08172566187670725</v>
+        <v>0.4275488739923725</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.009175805836997042</v>
+        <v>-0.06811167437199986</v>
       </c>
       <c r="DP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.007762230693009085</v>
+        <v>0.03512293954854934</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0.004370550438811952</v>
+        <v>0.06485841882675002</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.003769072133816353</v>
+        <v>0.02784623079434179</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.0171304898051085</v>
+        <v>-0.01956822445317299</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.02638448678380412</v>
+        <v>0.02253744081867776</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0007576852106967349</v>
+        <v>-0.1158573162066728</v>
       </c>
       <c r="EH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.006092441266440493</v>
+        <v>-0.1299797778367541</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.005075876730403864</v>
+        <v>0.1034701702532698</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
         <v>-0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.001326381987747497</v>
+        <v>-0.1009339474727254</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
@@ -2581,52 +2581,52 @@
         <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.0111904675766162</v>
+        <v>-0.1940716983663628</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.04990915605428066</v>
+        <v>0.1794861797306671</v>
       </c>
       <c r="EU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.01224630983234417</v>
+        <v>-0.1874765204252107</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.003706141976348104</v>
+        <v>-0.1025961347611617</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.03277681347753972</v>
+        <v>0.1649462496826471</v>
       </c>
       <c r="FD4" t="n">
         <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.01706457967047085</v>
+        <v>-0.1503023465122662</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
@@ -2635,64 +2635,64 @@
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.02663159863519494</v>
+        <v>-0.02753855480054997</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.007443367143096534</v>
+        <v>0.2290756907162116</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO4" t="n">
         <v>0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.009917963277520451</v>
+        <v>-0.009435874971548934</v>
       </c>
       <c r="FR4" t="n">
         <v>0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.02039883600591558</v>
+        <v>0.0253943745284437</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.03439207523210006</v>
+        <v>0.0258737853732565</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.03951519518675639</v>
+        <v>0.01034552025611947</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.005114592161808909</v>
+        <v>0.188486951927213</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,16 +2709,16 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2623000390108873</v>
+        <v>0.1686772532621242</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.04394310400635276</v>
+        <v>-0.04257207014840678</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.04793816206902284</v>
+        <v>-0.03240112029411406</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2733,19 +2733,19 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1952134476822699</v>
+        <v>0.1822613089471856</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.02482604018855934</v>
+        <v>-0.03755538140988942</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.09471758447412772</v>
+        <v>-0.07402306004376677</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2760,22 +2760,22 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03946899374733358</v>
+        <v>0.02515244996918898</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.01895576695664774</v>
+        <v>-0.007566405485667478</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.005938492599996444</v>
+        <v>-0.00107023479385855</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
@@ -2787,100 +2787,100 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.07228622801240109</v>
+        <v>-0.02595971046057203</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0103104450737678</v>
+        <v>-0.07100325358975028</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.07340543528590419</v>
+        <v>-0.0909374364222568</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.07851170760082661</v>
+        <v>0.1268030693383531</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.0887284919217302</v>
+        <v>-0.02000688692945369</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.1103975538658979</v>
+        <v>0.08393765530383</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3903362407442892</v>
+        <v>0.213744381306715</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.004932813572587539</v>
+        <v>-0.09449680735176952</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.108984117294115</v>
+        <v>-0.07740626839159113</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
         <v>-0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.007202717398464752</v>
+        <v>-0.01920368369770559</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.07266223469828109</v>
+        <v>-0.01098587089823441</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1386860321793579</v>
+        <v>-0.03847460337041642</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2895,25 +2895,25 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1206209217113547</v>
+        <v>-0.02284877447180678</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.1021472727122389</v>
+        <v>0.04248831442015674</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1417474652712359</v>
+        <v>0.08449016542613087</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,19 +2925,19 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.336736410163649</v>
+        <v>0.2659309236356017</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.05244766366930895</v>
+        <v>-0.1361455136405322</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.0325575644670176</v>
+        <v>-0.003515325492737882</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
@@ -2952,43 +2952,43 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1181505075850402</v>
+        <v>-0.1357072234925604</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.03987009495852072</v>
+        <v>0.08994194120698727</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.01139251490043524</v>
+        <v>0.01695389018487517</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.01460388571743329</v>
+        <v>-0.06008893533196324</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.02834185895159496</v>
+        <v>0.02883442782155592</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.09245362511497504</v>
+        <v>0.03019665193844972</v>
       </c>
       <c r="CR5" t="n">
         <v>0</v>
@@ -3000,22 +3000,22 @@
         <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1018371049564523</v>
+        <v>-0.1426898330169325</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0631607010408753</v>
+        <v>0.09938015258646853</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.00052486506482453</v>
+        <v>0.02573500355424193</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
@@ -3027,31 +3027,31 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.00417741921297577</v>
+        <v>-0.006300594718493526</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.05412419547756863</v>
+        <v>0.04192202430314292</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.08481765295658303</v>
+        <v>-0.08058588879664581</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
         <v>0</v>
@@ -3060,22 +3060,22 @@
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.1184930219119654</v>
+        <v>-0.06815864284358088</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.02481516720621864</v>
+        <v>0.03622798589480907</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.03285924999002392</v>
+        <v>-0.06699425875546056</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
         <v>-0</v>
@@ -3087,25 +3087,25 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.003550336817347432</v>
+        <v>0.08299429259582751</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.04362017165312296</v>
+        <v>0.05952486494391596</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.02813596691781599</v>
+        <v>-0.07000621732348909</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
         <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,100 +3114,100 @@
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.07617057120986434</v>
+        <v>-0.07560523437751161</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.01212427401939924</v>
+        <v>0.09869779874412676</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.08823086587778957</v>
+        <v>0.01630783825865042</v>
       </c>
       <c r="EK5" t="n">
         <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>-0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.08708667283692273</v>
+        <v>-0.09413277348901407</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.08596035939661163</v>
+        <v>0.08602143334042064</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.04393214362510548</v>
+        <v>-0.04579644169932604</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.09941576870021603</v>
+        <v>-0.1529116602380108</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.0678179565425289</v>
+        <v>0.1104035830673889</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.003849705498925376</v>
+        <v>0.005404068400217061</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.01947544419622893</v>
+        <v>-0.05056999225221973</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.1033401629635127</v>
+        <v>-0.00460070902707751</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.003891766409714157</v>
+        <v>0.04912299953469335</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
@@ -3216,25 +3216,25 @@
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.06591062012041043</v>
+        <v>0.03453705967631873</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.05102617737389269</v>
+        <v>0.175791044929674</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.04391761738832146</v>
+        <v>-0.06183737897411495</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
@@ -3246,28 +3246,28 @@
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.02456459038341135</v>
+        <v>-0.102237225179696</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.03913082021503059</v>
+        <v>0.03186788239571951</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>-0</v>
@@ -3275,10 +3275,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01669332478599372</v>
+        <v>0.03923058811553787</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,10 +3287,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.002572342346509499</v>
+        <v>0.03103129025400379</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.072060390821502e-11</v>
+        <v>-3.612803840527692e-11</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -3305,7 +3305,7 @@
         <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006193794217645182</v>
+        <v>0.07881161263750552</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.01045372093000241</v>
+        <v>0.01977104756035092</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.01005499695609202</v>
+        <v>-0.02395084496094973</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.001570964573375974</v>
+        <v>-0.00840691970625802</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,52 +3341,52 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.001773272391992953</v>
+        <v>-0.01431600657510333</v>
       </c>
       <c r="X6" t="n">
-        <v>7.380318802736919e-12</v>
+        <v>-2.729423127319506e-12</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.02034640794197507</v>
+        <v>-0.03616573937384744</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.02264062181210606</v>
+        <v>-0.06486083551905687</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.004152104925607843</v>
+        <v>-0.02908502662566952</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.001006301882205509</v>
+        <v>0.0128804572272651</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -3395,25 +3395,25 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01730849406253471</v>
+        <v>-0.007068546538503709</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.009022773393692904</v>
+        <v>-0.05492953211585069</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.03504173519999386</v>
+        <v>0.1172943476696262</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3422,10 +3422,10 @@
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.00443761616267909</v>
+        <v>-0.01406718644704287</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.006288269646586126</v>
+        <v>-0.02967908694144448</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0001048973379936943</v>
+        <v>-0.02129168614744807</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,52 +3449,52 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.01920653035594158</v>
+        <v>-0.0226692187043325</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.003144366615839003</v>
+        <v>-0.01019513542603069</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.02707565894038444</v>
+        <v>0.039150467678905</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.01628145744675088</v>
+        <v>0.05989964231971231</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.008329318506176599</v>
+        <v>0.05180931183190224</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.009806515242035619</v>
+        <v>0.07265561046706609</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.009064176822432378</v>
+        <v>-0.00768190535971407</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.02023325328088175</v>
+        <v>-0.07586362809792982</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,22 +3521,22 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.002135553193889004</v>
+        <v>-0.02009213297080004</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.001860095638370194</v>
+        <v>-0.009711842408165935</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.006019540295625784</v>
+        <v>0.04100209668732772</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3548,73 +3548,73 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.00565000140534183</v>
+        <v>-0.03705291461612636</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.005911088375860555</v>
+        <v>0.05680115356979313</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01228477105051659</v>
+        <v>0.03298265220527578</v>
       </c>
       <c r="CS6" t="n">
         <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.002882410745077564</v>
+        <v>-0.02266044022126278</v>
       </c>
       <c r="CX6" t="n">
         <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.001650156656204615</v>
+        <v>-0.01239441045350721</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.008242100621404529</v>
+        <v>0.03216545661253174</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.007033737953172504</v>
+        <v>-0.001576740370448926</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0003287304174156633</v>
+        <v>-0.002253417428652493</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.009897992422669848</v>
+        <v>0.0163110157413341</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,31 +3623,31 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.006732780452190565</v>
+        <v>-0.002990098071655361</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01559925814829154</v>
+        <v>-0.0004010166789318713</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.002677437602855399</v>
+        <v>0.05358450994783167</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV6" t="n">
         <v>-0</v>
@@ -3656,61 +3656,61 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.008566946315252821</v>
+        <v>-0.005152713222666326</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.005660220034970059</v>
+        <v>-0.02474495185218761</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.004352406671854736</v>
+        <v>0.01589883698100699</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.001933960480964549</v>
+        <v>-0.02799212122186942</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.0002588184761967825</v>
+        <v>-0.0394434288255973</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.007624794142424725</v>
+        <v>-0.0002718726815376628</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.004758901750781574</v>
+        <v>-0.006648592301740436</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
@@ -3719,40 +3719,40 @@
         <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.008680513144487733</v>
+        <v>-0.02293573800062193</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03668637984994976</v>
+        <v>0.03210011633928329</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.004747505823965433</v>
+        <v>-0.03029848663108601</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.003528193748113096</v>
+        <v>-0.0261722739579522</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.009958824721073449</v>
+        <v>0.03006227232424309</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
@@ -3761,10 +3761,10 @@
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.004323772120991413</v>
+        <v>-0.02920554807461711</v>
       </c>
       <c r="FI6" t="n">
         <v>0</v>
@@ -3773,25 +3773,25 @@
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.02046703226043356</v>
+        <v>0.003962244189213883</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.02156513814436725</v>
+        <v>-0.01911959982910008</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.008094034429320808</v>
+        <v>0.05300458719388975</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,10 +3800,10 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.000219222697643423</v>
+        <v>0.02011893880259771</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.003895634179216142</v>
+        <v>-0.03227484929568702</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3812,13 +3812,13 @@
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.02388244365757818</v>
+        <v>0.02470510464791512</v>
       </c>
       <c r="GA6" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.001012361404100634</v>
+        <v>0.01581348140329543</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1216245842937014</v>
+        <v>0.06829172764813971</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00262122735867466</v>
+        <v>-0.02456615646195834</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,22 +3868,22 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007429199901927578</v>
+        <v>0.002761408882541494</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06766298415917414</v>
+        <v>0.1244665063728828</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.06029221125564702</v>
+        <v>-0.03528950892451534</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,16 +3892,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.02793868521646546</v>
+        <v>-0.003171032440315343</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01782398521224272</v>
+        <v>-0.006914054128447695</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,52 +3910,52 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.01015883513918729</v>
+        <v>-0.02506361144119412</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-2.412063972189331e-14</v>
+        <v>-4.623125737507342e-13</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.06227988958226112</v>
+        <v>-0.0393358733024614</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.03975072117051515</v>
+        <v>-0.03249050949543898</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.02028707103027183</v>
+        <v>-0.001767428440710268</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.04624015927534422</v>
+        <v>0.03716585153103769</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02063542207814695</v>
+        <v>-0.01624044222960888</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.0290015311948419</v>
+        <v>-0.02296945785750045</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1782166982406451</v>
+        <v>0.1150363295355702</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1105112231690213</v>
+        <v>-0.01355489983581614</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,94 +4003,94 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.00242309760068584</v>
+        <v>0.01433969033790428</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.02448176422740797</v>
+        <v>-0.01481349770982844</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.08416124315413791</v>
+        <v>-0.03375491646461229</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.008427250066309214</v>
+        <v>-0.004889024534541508</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0003565786395974494</v>
+        <v>0.02155763926240855</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1387719505170871</v>
+        <v>0.05889338243563964</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0362157177325297</v>
+        <v>0.01930020779355851</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1471452169008871</v>
+        <v>0.09714447549876332</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.03020699456664742</v>
+        <v>-0.03873571175058154</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.01698176097234523</v>
+        <v>-0.02540043430194276</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.03878656430964367</v>
+        <v>-0.03756482082739001</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,10 +4099,10 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.005799838737515432</v>
+        <v>0.009912295612822298</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,25 +4111,25 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.03630489696122272</v>
+        <v>0.02056895565949872</v>
       </c>
       <c r="CM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.0117082895186639</v>
+        <v>-0.03854536334119066</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.03428815469553819</v>
+        <v>0.006057671800711557</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,13 +4138,13 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.001681642099201762</v>
+        <v>0.02728735073375235</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.03913656838435601</v>
+        <v>-0.03936111378181498</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,10 +4153,10 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.003907187585115118</v>
+        <v>0.004710891612702785</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
@@ -4165,121 +4165,121 @@
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.03355091179778973</v>
+        <v>0.01928399213029993</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.1520262578606214</v>
+        <v>-0.02921332489832382</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.05105168329553607</v>
+        <v>-0.009044164748457775</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.02826864936006567</v>
+        <v>-0.01112725673211082</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.02598722985145606</v>
+        <v>-0.01597593350119612</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.01028014356286097</v>
+        <v>0.009314962386962116</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0.0129569386730411</v>
+        <v>-0.03320648101003121</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.0192602756423587</v>
+        <v>0.02051086157443415</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.009243440616151776</v>
+        <v>-0.01360210163120302</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.01707853256457992</v>
+        <v>-1.470669382718344e-05</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.005012292182502016</v>
+        <v>-0.03199505757395976</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.02661047345908146</v>
+        <v>-0.0004212705340073062</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.04466840375613735</v>
+        <v>0.01321067821710597</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.07747111679989221</v>
+        <v>-0.009721879004933648</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
@@ -4288,25 +4288,25 @@
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.009851061919911938</v>
+        <v>-0.003993287911829488</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.01745053637562408</v>
+        <v>0.002995390602275618</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.04804085852634228</v>
+        <v>-0.04373598458694015</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,7 +4315,7 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.005325897720471686</v>
+        <v>-0.003376560669734392</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4327,22 +4327,22 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.02273934364984382</v>
+        <v>0.01949763432915138</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.05627213990910202</v>
+        <v>-0.03058211271058432</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.01003194121600693</v>
+        <v>-0.001203877653012906</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
@@ -4351,25 +4351,25 @@
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.04849298150293765</v>
+        <v>0.07204960834934099</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.09010216953502188</v>
+        <v>0.02404279360362779</v>
       </c>
       <c r="FR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS7" t="n">
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.02784495551877784</v>
+        <v>-0.02237120445716613</v>
       </c>
       <c r="FU7" t="n">
         <v>-0</v>
@@ -4378,16 +4378,16 @@
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0004879378887247773</v>
+        <v>-4.162145687046708e-05</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.07436989175476379</v>
+        <v>-0.01225074834439213</v>
       </c>
       <c r="GA7" t="n">
         <v>0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.0241950280369292</v>
+        <v>0.007475810939463317</v>
       </c>
     </row>
     <row r="8">
@@ -4985,16 +4985,16 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6730289103061521</v>
+        <v>0.1036904798775297</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2475452540881833</v>
+        <v>-0.0841059170239566</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.05782065985107303</v>
+        <v>-0.01176876128879615</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5009,19 +5009,19 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5205291058219838</v>
+        <v>0.1233308672410897</v>
       </c>
       <c r="L9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2662442607822327</v>
+        <v>-0.1445041226645755</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1100032792438557</v>
+        <v>-0.03778913837966267</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5039,25 +5039,25 @@
         <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0790589334174607</v>
+        <v>0.02918365610479776</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1028369059858262</v>
+        <v>-0.008565808163958877</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1376760270725572</v>
+        <v>-0.03455653167715332</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5066,22 +5066,22 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.2285295224738491</v>
+        <v>0.02071103302812403</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.02571502232946295</v>
+        <v>-0.07195657580338249</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.008985730714998261</v>
+        <v>-0.02811733147065565</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
@@ -5090,25 +5090,25 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1369960346384541</v>
+        <v>0.09967849552297979</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.09921103998815778</v>
+        <v>-0.09330300026342256</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.1772613352184149</v>
+        <v>0.06641073222411475</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>-0</v>
@@ -5120,16 +5120,16 @@
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.6392765788902598</v>
+        <v>0.1158255185592034</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.07365575896643503</v>
+        <v>-0.07810924395054321</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1028000219223276</v>
+        <v>-0.1266626675927031</v>
       </c>
       <c r="AY9" t="n">
         <v>-0</v>
@@ -5141,22 +5141,22 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.08115727839342819</v>
+        <v>-0.03379548569934125</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.07466542298349262</v>
+        <v>0.005463099825097591</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.2521964706911786</v>
+        <v>0.009892373391112192</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.2074132962939904</v>
+        <v>0.02043503382207388</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.08223392937517647</v>
+        <v>0.01223816888890238</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1779413294873264</v>
+        <v>0.001588658958448099</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,19 +5201,19 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.5448858485392473</v>
+        <v>0.157747346428146</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.1837799511573137</v>
+        <v>-0.1721785225476168</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.01911444824840426</v>
+        <v>-0.05443208723310884</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
@@ -5228,19 +5228,19 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.2139073660194432</v>
+        <v>-0.06248490370336716</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.05508961245554948</v>
+        <v>0.1136207314809434</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.06337935591065662</v>
+        <v>0.01035542840408157</v>
       </c>
       <c r="CI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ9" t="n">
         <v>-0</v>
@@ -5249,109 +5249,109 @@
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.02028627249818804</v>
+        <v>-0.05241778500313415</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.1705232537918879</v>
+        <v>0.1564015390387115</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.1151990480309028</v>
+        <v>0.05243025012538117</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.1768861313669184</v>
+        <v>-0.05087374241841065</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.1160018803158312</v>
+        <v>0.1219444164945394</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.02204519438313771</v>
+        <v>0.0201164411566798</v>
       </c>
       <c r="DA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.01864594380369006</v>
+        <v>-0.002589512258347409</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.185115890036977</v>
+        <v>0.02269042983725048</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.1604538132122105</v>
+        <v>-0.0367977339181188</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
         <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.1289916447984688</v>
+        <v>-0.06669554490061823</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.04158067056264217</v>
+        <v>0.08289305733470964</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.1167985215685362</v>
+        <v>0.01704629888024519</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5363,76 +5363,76 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.06221034092080683</v>
+        <v>0.01758758780080284</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.02188350774986661</v>
+        <v>0.04793279205091018</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.01327612842787099</v>
+        <v>-0.02146838267734841</v>
       </c>
       <c r="EB9" t="n">
         <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.08532915123000127</v>
+        <v>0.004925559812295312</v>
       </c>
       <c r="EH9" t="n">
         <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.04219664225249022</v>
+        <v>0.07919626146750046</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.06058343273354852</v>
+        <v>0.03399532284000357</v>
       </c>
       <c r="EK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.1900917937796626</v>
+        <v>-0.03502933174852057</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.1017796819783919</v>
+        <v>-0.08828685472410129</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.08031373487184915</v>
+        <v>-0.002607668012719437</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,73 +5444,73 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.1758779017442864</v>
+        <v>-0.06421390764685278</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.09776669461680272</v>
+        <v>0.1391209507347023</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.03368510467635981</v>
+        <v>0.007182626805304285</v>
       </c>
       <c r="FC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.07566143786837172</v>
+        <v>-0.04575035860521485</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.1121232844005494</v>
+        <v>0.03132908683565348</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.1173150275502451</v>
+        <v>-0.05049657851563503</v>
       </c>
       <c r="FL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.05546605198837567</v>
+        <v>0.05871413935554166</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.07175149643530726</v>
+        <v>0.1376665521647035</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.09612305313045955</v>
+        <v>-0.1107436880261306</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
@@ -5522,16 +5522,16 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.04927710721708611</v>
+        <v>-0.00975179856773377</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.03037615696268581</v>
+        <v>0.05810344896100893</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
@@ -5543,36 +5543,36 @@
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.2013540031721791</v>
+        <v>0.1657934373027016</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03758490039687784</v>
+        <v>-0.1641223191816378</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00920805541623638</v>
+        <v>-0.05870365614492716</v>
       </c>
       <c r="F10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01035451066417541</v>
+        <v>-0.01346855101328944</v>
       </c>
       <c r="I10" t="n">
         <v>-0</v>
@@ -5581,43 +5581,43 @@
         <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.02634257409880793</v>
+        <v>0.1607425165014447</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.08079098805350385</v>
+        <v>-0.2861218617270186</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1338543395178694</v>
+        <v>-0.1153746407790347</v>
       </c>
       <c r="O10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.0006598757360845318</v>
+        <v>1.829381609285409e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10" t="n">
         <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.05790662702065499</v>
+        <v>0.07917343143837995</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1016042433211437</v>
+        <v>-0.04566014854775466</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1134392308741438</v>
+        <v>-0.1095521136232591</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -5626,34 +5626,34 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.813571052869527e-11</v>
+        <v>-3.483923208990191e-12</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.08121128248318027</v>
+        <v>-0.06186403218961253</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.01752265502721575</v>
+        <v>-0.0592569587068518</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.08849873218162418</v>
+        <v>-0.1659149802396787</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.002027030514818985</v>
+        <v>0.02237615396164628</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
@@ -5662,79 +5662,79 @@
         <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.03808792974124892</v>
+        <v>0.1419600561575538</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.0673911121028386</v>
+        <v>-0.03939319480944044</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.1166721580805369</v>
+        <v>0.0495940068300213</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
         <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.05202091852855398</v>
+        <v>0.01675723714125532</v>
       </c>
       <c r="AS10" t="n">
         <v>-0</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.2888672085052906</v>
+        <v>0.1598027155822631</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.03602386178553146</v>
+        <v>-0.06805604674676367</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.1386048139562717</v>
+        <v>-0.2301629671464092</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0.1448239549622367</v>
+        <v>-0.02015931133144191</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0377874858649436</v>
+        <v>-0.04230295075703276</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.1380913589222375</v>
+        <v>-0.07348948864158593</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.1657643989868579</v>
+        <v>-0.05125732829360198</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.509422253670969e-11</v>
+        <v>2.279207323977877e-11</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -5743,16 +5743,16 @@
         <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0.3340369213352715</v>
+        <v>0.01705131033639447</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>-0.1456269617987496</v>
+        <v>0.1167950079295285</v>
       </c>
       <c r="BP10" t="n">
-        <v>-0.2266933473427629</v>
+        <v>-0.02123211351439067</v>
       </c>
       <c r="BQ10" t="n">
         <v>0</v>
@@ -5761,52 +5761,52 @@
         <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.04471488924518167</v>
+        <v>-0.004610373184168506</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>-0.2187673208558363</v>
+        <v>0.2194924044879295</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0.07266710644380285</v>
+        <v>-0.2032759281602317</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.06744763765097218</v>
+        <v>-0.1741009451476353</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.006220562784983018</v>
+        <v>-0.05564062196775691</v>
       </c>
       <c r="CC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD10" t="n">
         <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.03215716382470068</v>
+        <v>-0.05787273954528329</v>
       </c>
       <c r="CF10" t="n">
         <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.01126376976493424</v>
+        <v>0.1712834141569329</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.02587230533770108</v>
+        <v>0.03730615155147803</v>
       </c>
       <c r="CI10" t="n">
         <v>0</v>
@@ -5815,34 +5815,34 @@
         <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.02486007296587812</v>
+        <v>-0.0286057160531945</v>
       </c>
       <c r="CL10" t="n">
         <v>0</v>
       </c>
       <c r="CM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.034275462556146</v>
+        <v>-0.006296493345717069</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.03393312412654527</v>
+        <v>0.1103462557265263</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.05430610257776698</v>
+        <v>0.2093938952566736</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.02538300804569434</v>
+        <v>0.04215942563406992</v>
       </c>
       <c r="CU10" t="n">
         <v>-0</v>
@@ -5851,25 +5851,25 @@
         <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.002037126662049555</v>
+        <v>-0.0589415641001432</v>
       </c>
       <c r="CX10" t="n">
         <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>-0.01912035172000403</v>
+        <v>0.1847974365241757</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.002698821914440556</v>
+        <v>0.05129020019620979</v>
       </c>
       <c r="DA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.01865237057223328</v>
+        <v>-0.01555659150612083</v>
       </c>
       <c r="DD10" t="n">
         <v>-0</v>
@@ -5878,16 +5878,16 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.005791646238707438</v>
+        <v>-0.06687718413799081</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.00864743099045529</v>
+        <v>0.06347438841574367</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.01439886389136689</v>
+        <v>-0.003241971965393687</v>
       </c>
       <c r="DJ10" t="n">
         <v>-0</v>
@@ -5896,34 +5896,34 @@
         <v>0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0.03041978903957623</v>
+        <v>-0.0429667181025152</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.07105068858889727</v>
+        <v>-0.03460088147541669</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.01147413937772165</v>
+        <v>0.08127375102740687</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.05102670428712219</v>
+        <v>-0.07490322575335927</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>-0.1395987539161067</v>
+        <v>0.1065306935662125</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
@@ -5932,25 +5932,25 @@
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.1037982995182301</v>
+        <v>0.03365836367512578</v>
       </c>
       <c r="DY10" t="n">
         <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.02105702133002278</v>
+        <v>0.1040877472581454</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.1366083423960719</v>
+        <v>-0.1021687058217902</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
       </c>
       <c r="EC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0.05110927003315545</v>
+        <v>0.1460538428681828</v>
       </c>
       <c r="EE10" t="n">
         <v>-0</v>
@@ -5959,43 +5959,43 @@
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.02691503203185176</v>
+        <v>0.01398965218950729</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.05407312057582109</v>
+        <v>0.1427806846082859</v>
       </c>
       <c r="EJ10" t="n">
-        <v>-0.004795996983736483</v>
+        <v>0.02205206683344086</v>
       </c>
       <c r="EK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0257305306959912</v>
+        <v>-0.02829348563089955</v>
       </c>
       <c r="EN10" t="n">
         <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.03715577679205467</v>
+        <v>-0.04785655475274429</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0.05916873331795774</v>
+        <v>0.1503229337218286</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.09358093920103559</v>
+        <v>-0.01848612234199348</v>
       </c>
       <c r="ET10" t="n">
         <v>0</v>
@@ -6004,61 +6004,61 @@
         <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.1081630683884812</v>
+        <v>0.007367488529354454</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
         <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.001944547737660567</v>
+        <v>-0.07200027116637973</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0.000589668558557671</v>
+        <v>0.2087870694348537</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.04431715806466465</v>
+        <v>0.04849395854062038</v>
       </c>
       <c r="FC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD10" t="n">
         <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.04827079270555414</v>
+        <v>-0.02135958433394403</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.01030735962916447</v>
+        <v>-0.02935136222191148</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.01433163406797664</v>
+        <v>-0.04970044015835661</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.04232237450832357</v>
+        <v>0.05718273280431231</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM10" t="n">
         <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.04469348901950312</v>
+        <v>-0.04174981028744355</v>
       </c>
       <c r="FO10" t="n">
         <v>-0</v>
@@ -6067,16 +6067,16 @@
         <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.3051680217669358</v>
+        <v>0.05578975635720916</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.08097053152857363</v>
+        <v>0.2003810143594018</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.2715951877591075</v>
+        <v>-0.1640863655019329</v>
       </c>
       <c r="FU10" t="n">
         <v>0</v>
@@ -6085,84 +6085,84 @@
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.1007224361954855</v>
+        <v>-0.1131554192892302</v>
       </c>
       <c r="FX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY10" t="n">
         <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.06298102528413385</v>
+        <v>-0.004231283067356852</v>
       </c>
       <c r="GA10" t="n">
         <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.05089869411827275</v>
+        <v>0.09064369818721082</v>
       </c>
       <c r="GC10" t="n">
         <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0.01528977898486837</v>
+        <v>-0.05091978752662428</v>
       </c>
       <c r="GG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.004187303731417924</v>
+        <v>0.4092679476166792</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1490073197494882</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0003024649165285149</v>
+        <v>0.0261925454275147</v>
       </c>
       <c r="F11" t="n">
-        <v>-0</v>
+        <v>-0.3573593359716168</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
         <v>-0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.003840851418583203</v>
+        <v>0.5701234286811091</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.12414079695875</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0002001562238406988</v>
+        <v>-0.1213364796842791</v>
       </c>
       <c r="O11" t="n">
-        <v>-0</v>
+        <v>-0.4103323179732203</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -6171,25 +6171,25 @@
         <v>-0</v>
       </c>
       <c r="R11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.533844793161502e-11</v>
+        <v>0.1606981965694378</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.02268116723716583</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.898375168432205e-12</v>
+        <v>-0.1452036333819316</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.04016916003422871</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
@@ -6201,22 +6201,22 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.01415360279696495</v>
+        <v>-0.001917292757462457</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.01259529804034848</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0006848262435804358</v>
+        <v>-0.3935413381546858</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0</v>
+        <v>-0.03842485615138744</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6231,103 +6231,103 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.004908969585586187</v>
+        <v>0.2046820102405041</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.01684146765163013</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.06004168267354253</v>
+        <v>0.02984844734397298</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0</v>
+        <v>-0.09437214443161382</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.05111650592021327</v>
+        <v>0.4536047487136847</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.05047233790097302</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.005593163204241245</v>
+        <v>-0.1943249663337576</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0</v>
+        <v>-0.113777959760413</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.0004720937399618434</v>
+        <v>-0.04557157660285277</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.06335075853316964</v>
+        <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.119492569874074e-12</v>
+        <v>-0.1069620419696554</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>-0.1612598161327942</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
         <v>-0</v>
       </c>
       <c r="BK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
         <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.005667511666663855</v>
+        <v>0.08992693855527062</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>-0.04570669103352488</v>
+        <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>-0.08026561652163743</v>
+        <v>0.09062837651750157</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>0.03120260782387401</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>0</v>
@@ -6336,52 +6336,52 @@
         <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>-0.02721469782140242</v>
+        <v>0.4977419332633865</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.0148747189364788</v>
+        <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.002160216032024279</v>
+        <v>-0.1054484168945093</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0</v>
+        <v>-0.2268571601247106</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC11" t="n">
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.006961677468368214</v>
+        <v>-0.2081436806983372</v>
       </c>
       <c r="CF11" t="n">
         <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>-0.0294012837734784</v>
+        <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.01845334188041233</v>
+        <v>-0.006251914292118613</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>0.1577005980221635</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6390,49 +6390,49 @@
         <v>0</v>
       </c>
       <c r="CM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.002035822980452323</v>
+        <v>-0.197518523830431</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.0005434914360416356</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.03399546480740017</v>
+        <v>0.2044590979588035</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0</v>
+        <v>0.0950349614095969</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
         <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.0199520543710801</v>
+        <v>-0.174973826966529</v>
       </c>
       <c r="CX11" t="n">
         <v>0</v>
       </c>
       <c r="CY11" t="n">
-        <v>-0.02743534013505022</v>
+        <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.005657166466025781</v>
+        <v>-0.009887343710952855</v>
       </c>
       <c r="DA11" t="n">
-        <v>-0</v>
+        <v>0.1621018395293741</v>
       </c>
       <c r="DB11" t="n">
         <v>-0</v>
@@ -6441,52 +6441,52 @@
         <v>-0</v>
       </c>
       <c r="DD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.01917022669022506</v>
+        <v>-0.105642366708117</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.02442041932031243</v>
+        <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.007577054241339181</v>
+        <v>-0.2162805757222727</v>
       </c>
       <c r="DJ11" t="n">
-        <v>-0</v>
+        <v>0.01825344532253313</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM11" t="n">
         <v>-0</v>
       </c>
       <c r="DN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.02616255353576847</v>
+        <v>-0.1095994996057662</v>
       </c>
       <c r="DP11" t="n">
         <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.02370382361513589</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.01526535988272492</v>
+        <v>-0.01546871302913264</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0</v>
+        <v>0.06710288714543215</v>
       </c>
       <c r="DT11" t="n">
         <v>0</v>
@@ -6495,25 +6495,25 @@
         <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.04642558886926763</v>
+        <v>0.04976158874601991</v>
       </c>
       <c r="DY11" t="n">
         <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>-0.009896536257032731</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.02765923187151757</v>
+        <v>0.05852513895879677</v>
       </c>
       <c r="EB11" t="n">
-        <v>0</v>
+        <v>0.1473215746293224</v>
       </c>
       <c r="EC11" t="n">
         <v>-0</v>
@@ -6528,19 +6528,19 @@
         <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.01224944060790535</v>
+        <v>-0.00783723090332753</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.06342037664410527</v>
+        <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>-0.01500220555048973</v>
+        <v>-0.09643138712851378</v>
       </c>
       <c r="EK11" t="n">
-        <v>-0</v>
+        <v>0.1074641651389088</v>
       </c>
       <c r="EL11" t="n">
         <v>0</v>
@@ -6552,25 +6552,25 @@
         <v>0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.05093734714919251</v>
+        <v>-0.07429476303495833</v>
       </c>
       <c r="EQ11" t="n">
         <v>0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0.0178477251004682</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.03331384216807593</v>
+        <v>-0.1399126904620118</v>
       </c>
       <c r="ET11" t="n">
-        <v>0</v>
+        <v>0.1310520849233714</v>
       </c>
       <c r="EU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV11" t="n">
         <v>0</v>
@@ -6579,82 +6579,82 @@
         <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.02513192810633938</v>
+        <v>-0.2242781180202646</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>-0.02774116473546082</v>
+        <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01433112277992755</v>
+        <v>-0.02288009471156018</v>
       </c>
       <c r="FC11" t="n">
-        <v>0</v>
+        <v>0.1424375515701566</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.01674936558193549</v>
+        <v>-0.2399907104356502</v>
       </c>
       <c r="FI11" t="n">
         <v>0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>-0.003875702510505077</v>
+        <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.02090742738704613</v>
+        <v>0.1892806698336954</v>
       </c>
       <c r="FL11" t="n">
-        <v>-0</v>
+        <v>0.1449843636820508</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP11" t="n">
         <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.01196568547262348</v>
+        <v>0.1745648155300083</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
-        <v>-0.003171861189233906</v>
+        <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.01042584441762457</v>
+        <v>-0.01900812385695772</v>
       </c>
       <c r="FU11" t="n">
-        <v>0</v>
+        <v>0.1346766495335273</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
         <v>-0</v>
@@ -6663,19 +6663,19 @@
         <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.002817015083660806</v>
+        <v>-0.05690101502421802</v>
       </c>
       <c r="GA11" t="n">
         <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.02877200076449832</v>
+        <v>-0</v>
       </c>
       <c r="GC11" t="n">
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>0</v>
+        <v>0.101639779020603</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6692,25 +6692,25 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.3881329184776394</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0.1866447542652816</v>
       </c>
       <c r="E12" t="n">
-        <v>-0</v>
+        <v>-0.012220062718736</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -6719,22 +6719,22 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.4520578340987695</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>-0.2738429888654865</v>
       </c>
       <c r="N12" t="n">
-        <v>-0</v>
+        <v>-0.08607446781935504</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -6743,28 +6743,28 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.1072617963953201</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.06701976632506911</v>
       </c>
       <c r="W12" t="n">
-        <v>-0</v>
+        <v>-0.08518459316225484</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -6773,25 +6773,25 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>-0.1269423400873663</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>-0.1147389069248308</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0</v>
+        <v>-0.1119172111548615</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
@@ -6800,16 +6800,16 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>0.1693661699020807</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>-0.1273797759091338</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0</v>
+        <v>0.102118641216407</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6818,7 +6818,7 @@
         <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
@@ -6827,19 +6827,19 @@
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>0.2388097612279838</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>-0.08268542606315071</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0</v>
+        <v>-0.09992549782532842</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -6848,49 +6848,49 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>-0.01649191907523872</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>-0.04708662073183938</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0</v>
+        <v>-0.08111763387285012</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>-0.02981415456997016</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>0.02708005087366439</v>
       </c>
       <c r="BP12" t="n">
-        <v>-0</v>
+        <v>0.07319388570565463</v>
       </c>
       <c r="BQ12" t="n">
         <v>0</v>
@@ -6899,31 +6899,31 @@
         <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>0.3384672416595387</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>-0.186092554154648</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0</v>
+        <v>-0.01755150409818111</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
         <v>0</v>
@@ -6932,19 +6932,19 @@
         <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>0</v>
+        <v>-0.1627584832761302</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0</v>
+        <v>0.1571568176765238</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0</v>
+        <v>-0.006324229485295144</v>
       </c>
       <c r="CI12" t="n">
         <v>0</v>
@@ -6956,58 +6956,58 @@
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>0</v>
+        <v>-0.05463023784753388</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0</v>
+        <v>0.2002807681495089</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0</v>
+        <v>0.03756042369499799</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>0</v>
+        <v>-0.1501590790260707</v>
       </c>
       <c r="CX12" t="n">
         <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0</v>
+        <v>0.1584528800966928</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0</v>
+        <v>0.01325973031738214</v>
       </c>
       <c r="DA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
@@ -7016,19 +7016,19 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>0</v>
+        <v>-0.1251667465039433</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0</v>
+        <v>0.02919238292403675</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0</v>
+        <v>-0.103472360621447</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
         <v>0</v>
@@ -7040,73 +7040,73 @@
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>0</v>
+        <v>-0.09323307846173623</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0</v>
+        <v>0.08199853207852419</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0</v>
+        <v>-0.0007001844526628761</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0</v>
+        <v>0.01506649281926625</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0</v>
+        <v>-0.07381990051720298</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0</v>
+        <v>0.0418588449478088</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
         <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>0</v>
+        <v>-0.09980779372629631</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0</v>
+        <v>0.1355655019527475</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0</v>
+        <v>0.04161580052237774</v>
       </c>
       <c r="EK12" t="n">
         <v>0</v>
@@ -7118,25 +7118,25 @@
         <v>0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>0</v>
+        <v>-0.1020990798086861</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0</v>
+        <v>0.09515857302969936</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0</v>
+        <v>-0.04117919771671163</v>
       </c>
       <c r="ET12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU12" t="n">
         <v>0</v>
@@ -7145,25 +7145,25 @@
         <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>0</v>
+        <v>-0.1716551950714346</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0</v>
+        <v>0.1826192787294632</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0</v>
+        <v>-0.01808406124920333</v>
       </c>
       <c r="FC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD12" t="n">
         <v>0</v>
@@ -7172,88 +7172,4640 @@
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0</v>
+        <v>-0.122793640312773</v>
       </c>
       <c r="FI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0</v>
+        <v>0.08388903463818459</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0</v>
+        <v>-0.01131096904598479</v>
       </c>
       <c r="FL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0</v>
+        <v>0.01694114599376048</v>
       </c>
       <c r="FR12" t="n">
         <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0</v>
+        <v>0.1870365199377353</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0</v>
+        <v>0.03690663845536515</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
         <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
         <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0</v>
+        <v>-0.1381795744565812</v>
       </c>
       <c r="GA12" t="n">
         <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>0</v>
+        <v>0.1098385360893862</v>
       </c>
       <c r="GC12" t="n">
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.1832684358565236</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.001622207620423347</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2466376807613374</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.2241123651862089</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.08287506306231153</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.2338543877930077</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.1009560397727116</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.1052202202035706</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.02616790467908605</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.01296442481841628</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.2421860286773792</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.1626957610848994</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-0.1184017956903107</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.07936998901302851</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.1104029130118591</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-0.2098522949537567</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.04189844454071181</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.05954006868089625</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.06286851844403976</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.206310638484433</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0.1909984007897451</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.02456679092285581</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-0.07385393719117438</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>-0.01501568652483533</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>-0.2621292377165296</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.02933384777530557</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0.1630791692441616</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.1083671453469329</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>-0.01194532847207062</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>-0.1050657969787537</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.1171418493072607</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>-0.1882597452373118</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>-0.1202423885810903</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.1019273818065752</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>-0.01201614358172045</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>-0.09607706739146131</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0.05218118635720746</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.1166312853462272</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>-0.0335492714131294</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0.06240762294212251</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.0192980484653614</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>-0.04491024566076672</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>-0.02868592672866155</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.01444393365280076</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>-0.08353436526313668</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.0458366887592434</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>0.0228425149541371</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>-0.04285565310075368</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>0.03803942454369612</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.02961018311877085</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>-0.075522317086001</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0.1190688202177901</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>-0.006046084205280827</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>-0.09657505321966979</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.1368377447205533</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>-0.0542561451673641</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0.0490401571342557</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>-0.03495023985183451</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>-0.02038542681334109</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0.05305622359791858</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>0.06781183608233335</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>-0.001869830388145074</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0.1223246914980979</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.2688193758594173</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.08424579308079566</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.0906128969599148</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.3802903431279998</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.04591943480966535</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.009650772229820354</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.04190427468069349</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.07326190683975495</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.03622966281083643</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.04668549540212714</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.1769280844303295</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.03637400319010111</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-0.1501745319639742</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.03864964881062798</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-0.05048402852936237</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-0.2318248965271362</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.03340585133614097</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.1722466782496892</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0.2048574222992905</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.1810709116099381</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>-0.008950108795428366</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0.01598548600085856</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-0.101607436205002</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0.0597987315206157</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>-0.283704022965012</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>-0.06018008948713751</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>-0.05609838613296238</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.125115949258008</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>-0.02004965860647237</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>-0.001820354542011168</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0.1581544287574745</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>-0.03999002272466943</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>-0.04667605290260841</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0.1299677666765862</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>-0.005961863346114537</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>-0.01511296400608977</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0.1193906204369399</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>-0.01626687382677938</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>-0.05819773666455091</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>-0.013204396302907</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>0.007465003000759433</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0.007897147979023791</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>0.03305738867955773</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0.02374843901269949</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>-0.09807313513778525</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>0.1026259411354636</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.02127579658287778</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0.03416734739682314</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>0.121935496103515</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>0.004018800535751024</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>-0.05369541614773207</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>0.1609216509833315</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>-0.0128994932495127</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0.02004867264870381</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>0.1067044856770567</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0.1164424821521183</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>-0.009360376689764733</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>0.2383644963839864</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0.05376954095099896</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0.02643201232606797</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>0.1847183136010742</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.3121043316794853</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.184019284975318</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.03378536098805632</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.3591915850314906</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.2783964997430957</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.0878685364811217</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.0380960622250848</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-0.05137175686774264</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.06278422403035182</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.06563353054360498</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-0.09456558606633772</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.0698394764455869</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.08795823378874479</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-0.1028713373306099</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.05666189831315637</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0.1697071946801623</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-0.01501181972396894</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0.08006731391741752</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-0.003070013568423678</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-0.04485084421470277</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-0.0369619262244832</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>-0.001475652692024871</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0.05809521543209168</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0.05478733781749651</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0.1907062378705801</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>-0.1317074668093271</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>-0.01357187300725568</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>-0.09454179449512824</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0.09763318152045196</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>-0.0002973619674629417</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>-0.08144963146986899</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>0.1679018074681726</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>0.03132497602710863</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>-0.09355666401712889</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>0.099378766500774</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>0.01380752513915604</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>-0.06345366157278713</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0.03571511416121263</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>-0.07590262339128521</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>-0.05543915775659777</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>-0.02642413480002574</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>-0.02040894314118773</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>0.00631539590791465</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ17" t="n">
+        <v>0.0788237944087968</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>-0.03984460111569511</v>
+      </c>
+      <c r="EB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG17" t="n">
+        <v>-0.07210233591956584</v>
+      </c>
+      <c r="EH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI17" t="n">
+        <v>0.06287233268957149</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>0.05446504762763127</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP17" t="n">
+        <v>-0.03864666806296</v>
+      </c>
+      <c r="EQ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER17" t="n">
+        <v>0.06049923917087396</v>
+      </c>
+      <c r="ES17" t="n">
+        <v>-0.01259371544932154</v>
+      </c>
+      <c r="ET17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY17" t="n">
+        <v>-0.1055896638417474</v>
+      </c>
+      <c r="EZ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA17" t="n">
+        <v>0.1196218666309606</v>
+      </c>
+      <c r="FB17" t="n">
+        <v>-0.004178597347161471</v>
+      </c>
+      <c r="FC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH17" t="n">
+        <v>0.1045278727081716</v>
+      </c>
+      <c r="FI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ17" t="n">
+        <v>0.07386799721186725</v>
+      </c>
+      <c r="FK17" t="n">
+        <v>-0.01638936349046422</v>
+      </c>
+      <c r="FL17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ17" t="n">
+        <v>0.04487902704438904</v>
+      </c>
+      <c r="FR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS17" t="n">
+        <v>0.1231973104888502</v>
+      </c>
+      <c r="FT17" t="n">
+        <v>-0.0246407529710801</v>
+      </c>
+      <c r="FU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ17" t="n">
+        <v>-0.05500113682269256</v>
+      </c>
+      <c r="GA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB17" t="n">
+        <v>0.0335210706371262</v>
+      </c>
+      <c r="GC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG17" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.1922327151719048</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.1173416294569894</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3740935343366819</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.2430710566143981</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.1205665824394074</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.510731808185066</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.09974144106645126</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.1258338397245696</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.04896602488198107</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.02745743359691321</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.2922166073056737</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.04446532589150534</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-0.03123158408713943</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.02057215120041412</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.02716870398127046</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>-0.05771865049762105</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.05127800594147884</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.2207757232358361</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0.06994396686862392</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0.1163484940148367</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0.01323226363398383</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>-0.08972725964102679</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-0.1303348831209825</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>-0.01486857056007685</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>-0.2139258871525834</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0.02355147544682972</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0.1789762286568501</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.04593660581330667</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>-0.0456093072635134</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>-0.1088250820027643</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0.1080935793591926</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>-0.08178315819161308</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>-0.06134001129352391</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>0.04369456701248584</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>-0.06003452082277065</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>-0.1361530825939004</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>0.03987003956127635</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>0.0956084659765168</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>-0.06558801966008844</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>-0.08751526224802172</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>0.08942746898111506</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>-0.0214851354256088</v>
+      </c>
+      <c r="DT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX18" t="n">
+        <v>0.08496455355781221</v>
+      </c>
+      <c r="DY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA18" t="n">
+        <v>0.0853113425774331</v>
+      </c>
+      <c r="EB18" t="n">
+        <v>-0.05261680461443655</v>
+      </c>
+      <c r="EC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG18" t="n">
+        <v>0.03107927437867854</v>
+      </c>
+      <c r="EH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ18" t="n">
+        <v>-0.0646027458863451</v>
+      </c>
+      <c r="EK18" t="n">
+        <v>-0.01079211259794421</v>
+      </c>
+      <c r="EL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP18" t="n">
+        <v>0.008155661080140221</v>
+      </c>
+      <c r="EQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES18" t="n">
+        <v>-0.09970730745131494</v>
+      </c>
+      <c r="ET18" t="n">
+        <v>-0.1799907397380341</v>
+      </c>
+      <c r="EU18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY18" t="n">
+        <v>0.06100876968039556</v>
+      </c>
+      <c r="EZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB18" t="n">
+        <v>-0.02775496706424986</v>
+      </c>
+      <c r="FC18" t="n">
+        <v>-0.103546701977163</v>
+      </c>
+      <c r="FD18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH18" t="n">
+        <v>-0.1039414227990873</v>
+      </c>
+      <c r="FI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK18" t="n">
+        <v>0.0745146311279745</v>
+      </c>
+      <c r="FL18" t="n">
+        <v>-0.1391441654201315</v>
+      </c>
+      <c r="FM18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ18" t="n">
+        <v>-0.03603008795652334</v>
+      </c>
+      <c r="FR18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT18" t="n">
+        <v>0.1749523117467998</v>
+      </c>
+      <c r="FU18" t="n">
+        <v>0.05574630785169768</v>
+      </c>
+      <c r="FV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ18" t="n">
+        <v>0.0711598318647865</v>
+      </c>
+      <c r="GA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD18" t="n">
+        <v>-0.06349928948594516</v>
+      </c>
+      <c r="GE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG18" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>0</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER19" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.3972484394422824</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.07751982050000164</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.1869664620810409</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.4851125363067149</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.2984637878694041</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-0.1585459423382693</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.129110396135131</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.03643304936059442</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.07647733856314932</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-0.1292056745204887</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-0.1139054945070664</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>-0.005649453240463975</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.09712933838834438</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.09055673234399328</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>-0.05019224013838068</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0.5658714124240437</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>-0.1328502112038152</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>-0.03521479393168891</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>-0.1763154014279456</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>-0.05369795773033104</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>-0.09666970647090474</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0.001499550871266827</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0.1417610600977513</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0.08831743771471048</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>0.2868488350006033</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>-0.04299183894004955</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC20" t="n">
+        <v>-0.1213112391020623</v>
+      </c>
+      <c r="CD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE20" t="n">
+        <v>-0.1142101934843069</v>
+      </c>
+      <c r="CF20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH20" t="n">
+        <v>0.08651756966475645</v>
+      </c>
+      <c r="CI20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>0.0466289140984788</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN20" t="n">
+        <v>-0.09759662631104477</v>
+      </c>
+      <c r="CO20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ20" t="n">
+        <v>0.158373514969134</v>
+      </c>
+      <c r="CR20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU20" t="n">
+        <v>0.03103408496647131</v>
+      </c>
+      <c r="CV20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW20" t="n">
+        <v>-0.1111175883412078</v>
+      </c>
+      <c r="CX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ20" t="n">
+        <v>0.06766646396056296</v>
+      </c>
+      <c r="DA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD20" t="n">
+        <v>0.05999042869132674</v>
+      </c>
+      <c r="DE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF20" t="n">
+        <v>-0.05296988490524956</v>
+      </c>
+      <c r="DG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI20" t="n">
+        <v>-0.2009346922638531</v>
+      </c>
+      <c r="DJ20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM20" t="n">
+        <v>0.03178058088239881</v>
+      </c>
+      <c r="DN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO20" t="n">
+        <v>0.0134925988985384</v>
+      </c>
+      <c r="DP20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR20" t="n">
+        <v>-0.1441182852724211</v>
+      </c>
+      <c r="DS20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV20" t="n">
+        <v>0.03590181399332881</v>
+      </c>
+      <c r="DW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX20" t="n">
+        <v>-0.03629751030757124</v>
+      </c>
+      <c r="DY20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA20" t="n">
+        <v>-0.05157505965975167</v>
+      </c>
+      <c r="EB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE20" t="n">
+        <v>0.1000563129750991</v>
+      </c>
+      <c r="EF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG20" t="n">
+        <v>-0.06612456931630738</v>
+      </c>
+      <c r="EH20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ20" t="n">
+        <v>0.02853241028601594</v>
+      </c>
+      <c r="EK20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN20" t="n">
+        <v>0.01112651788372111</v>
+      </c>
+      <c r="EO20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP20" t="n">
+        <v>-0.01479729055162927</v>
+      </c>
+      <c r="EQ20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES20" t="n">
+        <v>-0.1047466775645905</v>
+      </c>
+      <c r="ET20" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW20" t="n">
+        <v>0.07981605244772098</v>
+      </c>
+      <c r="EX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY20" t="n">
+        <v>-0.1224231171847107</v>
+      </c>
+      <c r="EZ20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB20" t="n">
+        <v>0.04643114500285379</v>
+      </c>
+      <c r="FC20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF20" t="n">
+        <v>0.05471012684275349</v>
+      </c>
+      <c r="FG20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH20" t="n">
+        <v>-0.141759749746538</v>
+      </c>
+      <c r="FI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK20" t="n">
+        <v>0.0924128229667279</v>
+      </c>
+      <c r="FL20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO20" t="n">
+        <v>0.02051266658297543</v>
+      </c>
+      <c r="FP20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ20" t="n">
+        <v>-0.2323593016816525</v>
+      </c>
+      <c r="FR20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT20" t="n">
+        <v>0.08252580765744161</v>
+      </c>
+      <c r="FU20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX20" t="n">
+        <v>0.01262618917563804</v>
+      </c>
+      <c r="FY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ20" t="n">
+        <v>-0.04100686401847631</v>
+      </c>
+      <c r="GA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG20" t="n">
+        <v>-0.01238044641746</v>
       </c>
     </row>
   </sheetData>
